--- a/public/exports-from-60/29188548.xlsx
+++ b/public/exports-from-60/29188548.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319187</t>
+          <t xml:space="preserve">311319196</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">

--- a/public/exports-from-60/29188548.xlsx
+++ b/public/exports-from-60/29188548.xlsx
@@ -17314,7 +17314,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319196</t>
+          <t xml:space="preserve">311319187</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">

--- a/public/exports-from-60/29188548.xlsx
+++ b/public/exports-from-60/29188548.xlsx
@@ -4241,17 +4241,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 35</t>
+          <t xml:space="preserve">Blomsterhaven 1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224218</t>
+          <t xml:space="preserve">7849067</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4260,21 +4260,21 @@
         </is>
       </c>
       <c r="J57">
-        <v>62</v>
+        <v>650</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253139</t>
+          <t xml:space="preserve">311255453</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-12</t>
+          <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterhaven 1</t>
+          <t xml:space="preserve">Blomsterhaven 11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J58">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blomsterhaven 11</t>
+          <t xml:space="preserve">Buskevej 1A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,20 +4401,20 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7849067</t>
+          <t xml:space="preserve">264659, 264660</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J59">
-        <v>650</v>
+        <v>1268</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255453</t>
+          <t xml:space="preserve">311255458</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buskevej 1A</t>
+          <t xml:space="preserve">Kirsebærhaven 12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,20 +4476,20 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">264659, 264660</t>
+          <t xml:space="preserve">2222525</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J60">
-        <v>1268</v>
+        <v>180</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255458</t>
+          <t xml:space="preserve">311255463</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 12</t>
+          <t xml:space="preserve">Kirsebærhaven 18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4556,11 +4556,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J61">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 18</t>
+          <t xml:space="preserve">Kirsebærhaven 2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 2</t>
+          <t xml:space="preserve">Kirsebærhaven 26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4706,11 +4706,11 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J63">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 26</t>
+          <t xml:space="preserve">Møllebjergvej 28</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,20 +4776,20 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222525</t>
+          <t xml:space="preserve">2223209</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J64">
-        <v>200</v>
+        <v>341</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255463</t>
+          <t xml:space="preserve">311255469</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebjergvej 28</t>
+          <t xml:space="preserve">Præstegårdsvej 3A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223209</t>
+          <t xml:space="preserve">264614, 264615</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4860,11 +4860,11 @@
         </is>
       </c>
       <c r="J65">
-        <v>341</v>
+        <v>392</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255469</t>
+          <t xml:space="preserve">311255468</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præstegårdsvej 3A</t>
+          <t xml:space="preserve">Tolstrupvej 30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">264614, 264615</t>
+          <t xml:space="preserve">2232068</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>392</v>
+        <v>142</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255468</t>
+          <t xml:space="preserve">311255467</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4991,17 +4991,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolstrupvej 30</t>
+          <t xml:space="preserve">Gershøjvej 111</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2232068</t>
+          <t xml:space="preserve">2221130</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,21 +5010,21 @@
         </is>
       </c>
       <c r="J67">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255467</t>
+          <t xml:space="preserve">311256397</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-21</t>
+          <t xml:space="preserve">2027-06-26</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,17 +5066,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gershøjvej 111</t>
+          <t xml:space="preserve">Grønager 2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221130</t>
+          <t xml:space="preserve">2221510</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,16 +5085,16 @@
         </is>
       </c>
       <c r="J68">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256397</t>
+          <t xml:space="preserve">311256384</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønager 2</t>
+          <t xml:space="preserve">Bognæsvej 11A</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,20 +5151,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221510</t>
+          <t xml:space="preserve">2172366</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J69">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256384</t>
+          <t xml:space="preserve">311256753</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-26</t>
+          <t xml:space="preserve">2027-06-27</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bognæsvej 11A</t>
+          <t xml:space="preserve">Bognæsvej 11C</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J70">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bognæsvej 11C</t>
+          <t xml:space="preserve">Bognæsvej 11E</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J71">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bognæsvej 11E</t>
+          <t xml:space="preserve">Bognæsvej 5A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5381,11 +5381,11 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J72">
-        <v>120</v>
+        <v>255</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bognæsvej 5A</t>
+          <t xml:space="preserve">Bognæsvej 9B</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5456,15 +5456,15 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J73">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256753</t>
+          <t xml:space="preserve">311256757</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bognæsvej 9B</t>
+          <t xml:space="preserve">Byvejen 35A</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172366</t>
+          <t xml:space="preserve">2227064</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J74">
-        <v>259</v>
+        <v>131</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256757</t>
+          <t xml:space="preserve">311256747</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvejen 35A</t>
+          <t xml:space="preserve">Hornsherredvej 437</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2227064</t>
+          <t xml:space="preserve">2231992</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5610,16 +5610,16 @@
         </is>
       </c>
       <c r="J75">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256747</t>
+          <t xml:space="preserve">311256729</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornsherredvej 437</t>
+          <t xml:space="preserve">Horseager 6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231992</t>
+          <t xml:space="preserve">2222759</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,16 +5685,16 @@
         </is>
       </c>
       <c r="J76">
-        <v>180</v>
+        <v>554</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256729</t>
+          <t xml:space="preserve">311256834</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5756,15 +5756,15 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J77">
-        <v>554</v>
+        <v>273</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256834</t>
+          <t xml:space="preserve">311256835</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,35 +5816,35 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horseager 6</t>
+          <t xml:space="preserve">Karlebyvej 54A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222759</t>
+          <t xml:space="preserve">2225586</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J78">
-        <v>273</v>
+        <v>123</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256835</t>
+          <t xml:space="preserve">311256725</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlebyvej 54A</t>
+          <t xml:space="preserve">Karlebyvej 54C</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225586</t>
+          <t xml:space="preserve">2225587</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,11 +5910,11 @@
         </is>
       </c>
       <c r="J79">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256725</t>
+          <t xml:space="preserve">311256727</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,17 +5966,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlebyvej 54C</t>
+          <t xml:space="preserve">Langetoften 17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225587</t>
+          <t xml:space="preserve">2226625</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,11 +5985,11 @@
         </is>
       </c>
       <c r="J80">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256727</t>
+          <t xml:space="preserve">311256732</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,40 +6041,40 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 17</t>
+          <t xml:space="preserve">Kirsebærhaven 15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226625</t>
+          <t xml:space="preserve">2222525</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J81">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311256732</t>
+          <t xml:space="preserve">311257068</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-27</t>
+          <t xml:space="preserve">2027-06-28</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 15</t>
+          <t xml:space="preserve">Kirsebærhaven 19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J82">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 19</t>
+          <t xml:space="preserve">Kirsebærhaven 23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J83">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 23</t>
+          <t xml:space="preserve">Kirsebærhaven 3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J84">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 3</t>
+          <t xml:space="preserve">Kirsebærhaven 32</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J85">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 32</t>
+          <t xml:space="preserve">Kirsebærhaven 7</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J86">
@@ -6491,40 +6491,40 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirsebærhaven 7</t>
+          <t xml:space="preserve">Bygmarken 78</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222525</t>
+          <t xml:space="preserve">2231003</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J87">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257068</t>
+          <t xml:space="preserve">311258453</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-28</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,17 +6566,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygmarken 78</t>
+          <t xml:space="preserve">Langetoften 13A</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2231003</t>
+          <t xml:space="preserve">2226627</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,11 +6585,11 @@
         </is>
       </c>
       <c r="J88">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258453</t>
+          <t xml:space="preserve">311258486</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6641,17 +6641,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 13A</t>
+          <t xml:space="preserve">Engvej 5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226627</t>
+          <t xml:space="preserve">2226064</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,11 +6660,11 @@
         </is>
       </c>
       <c r="J89">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258486</t>
+          <t xml:space="preserve">311258899</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 5</t>
+          <t xml:space="preserve">Langetoften 12A</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226064</t>
+          <t xml:space="preserve">2226637</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6735,11 +6735,11 @@
         </is>
       </c>
       <c r="J90">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258899</t>
+          <t xml:space="preserve">311259010</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-07-05</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 12A</t>
+          <t xml:space="preserve">Oldvejen 2</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226637</t>
+          <t xml:space="preserve">9826008</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="J91">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259010</t>
+          <t xml:space="preserve">311259007</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oldvejen 2</t>
+          <t xml:space="preserve">Nordre Ryevej 52</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">9826008</t>
+          <t xml:space="preserve">2228828</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J92">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259007</t>
+          <t xml:space="preserve">311264700</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-05</t>
+          <t xml:space="preserve">2027-08-07</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,35 +6941,35 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ryevej 52</t>
+          <t xml:space="preserve">Roskildevej 9B</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228828</t>
+          <t xml:space="preserve">2222449</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J93">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264700</t>
+          <t xml:space="preserve">311264717</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -7031,11 +7031,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J94">
-        <v>66</v>
+        <v>141</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roskildevej 9B</t>
+          <t xml:space="preserve">Sandbechs Alle 10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,25 +7101,25 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222449</t>
+          <t xml:space="preserve">2222412</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J95">
-        <v>141</v>
+        <v>481</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264717</t>
+          <t xml:space="preserve">311264703</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandbechs Alle 10</t>
+          <t xml:space="preserve">Østergade 1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222412</t>
+          <t xml:space="preserve">2222357</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7185,16 +7185,16 @@
         </is>
       </c>
       <c r="J96">
-        <v>481</v>
+        <v>538</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264703</t>
+          <t xml:space="preserve">311264716</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 1</t>
+          <t xml:space="preserve">Bygaden 28A</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222357</t>
+          <t xml:space="preserve">2223861</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7260,21 +7260,21 @@
         </is>
       </c>
       <c r="J97">
-        <v>538</v>
+        <v>250</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311264716</t>
+          <t xml:space="preserve">311266807</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-07</t>
+          <t xml:space="preserve">2027-08-17</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28A</t>
+          <t xml:space="preserve">Tølløsevej 3C</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223861</t>
+          <t xml:space="preserve">2222957</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>250</v>
+        <v>339</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266807</t>
+          <t xml:space="preserve">311266810</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tølløsevej 3C</t>
+          <t xml:space="preserve">Møllebjergvej 6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222957</t>
+          <t xml:space="preserve">8286769</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,21 +7410,21 @@
         </is>
       </c>
       <c r="J99">
-        <v>339</v>
+        <v>732</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311266810</t>
+          <t xml:space="preserve">311267042</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-17</t>
+          <t xml:space="preserve">2027-08-18</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebjergvej 6</t>
+          <t xml:space="preserve">Skovvej 14</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8286769</t>
+          <t xml:space="preserve">2222867</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7485,11 +7485,11 @@
         </is>
       </c>
       <c r="J100">
-        <v>732</v>
+        <v>341</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267042</t>
+          <t xml:space="preserve">311267039</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7541,17 +7541,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 14</t>
+          <t xml:space="preserve">Rynkebjerggårdsvej 61</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222867</t>
+          <t xml:space="preserve">2218253</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7560,21 +7560,21 @@
         </is>
       </c>
       <c r="J101">
-        <v>341</v>
+        <v>678</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267039</t>
+          <t xml:space="preserve">311267861</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-18</t>
+          <t xml:space="preserve">2027-08-22</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7631,11 +7631,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J102">
-        <v>678</v>
+        <v>120</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rynkebjerggårdsvej 61</t>
+          <t xml:space="preserve">Rynkebjerggårdsvej 63</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7706,15 +7706,15 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J103">
-        <v>120</v>
+        <v>597</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267861</t>
+          <t xml:space="preserve">311267862</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7766,35 +7766,35 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rynkebjerggårdsvej 63</t>
+          <t xml:space="preserve">Sandbechs Alle 1A</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2218253</t>
+          <t xml:space="preserve">2222744</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J104">
-        <v>597</v>
+        <v>419</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267862</t>
+          <t xml:space="preserve">311267863</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandbechs Alle 1A</t>
+          <t xml:space="preserve">Hyldebjerg 72</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222744</t>
+          <t xml:space="preserve">9307053</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,21 +7860,21 @@
         </is>
       </c>
       <c r="J105">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311267863</t>
+          <t xml:space="preserve">311268972</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-22</t>
+          <t xml:space="preserve">2027-08-28</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldebjerg 72</t>
+          <t xml:space="preserve">Fyrrevænget 8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">9307053</t>
+          <t xml:space="preserve">2229465</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>81</v>
+        <v>220</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311268972</t>
+          <t xml:space="preserve">311271601</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-28</t>
+          <t xml:space="preserve">2027-09-07</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,17 +7991,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrrevænget 8</t>
+          <t xml:space="preserve">Sandbechs Alle 2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229465</t>
+          <t xml:space="preserve">2222421</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8010,11 +8010,11 @@
         </is>
       </c>
       <c r="J107">
-        <v>220</v>
+        <v>101</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271601</t>
+          <t xml:space="preserve">311271574</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,40 +8066,40 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandbechs Alle 2</t>
+          <t xml:space="preserve">Langetoften 11A</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222421</t>
+          <t xml:space="preserve">2226614</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J108">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311271574</t>
+          <t xml:space="preserve">311272660</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-07</t>
+          <t xml:space="preserve">2027-09-13</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11A</t>
+          <t xml:space="preserve">Langetoften 11C</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J109">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11C</t>
+          <t xml:space="preserve">Langetoften 11E</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J110">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11E</t>
+          <t xml:space="preserve">Langetoften 11H</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J111">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11H</t>
+          <t xml:space="preserve">Langetoften 11M</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8381,11 +8381,11 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J112">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 11M</t>
+          <t xml:space="preserve">Langetoften 7A</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8456,15 +8456,15 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J113">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272660</t>
+          <t xml:space="preserve">311272658</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7A</t>
+          <t xml:space="preserve">Langetoften 7D</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J114">
-        <v>219</v>
+        <v>149</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7D</t>
+          <t xml:space="preserve">Langetoften 7F</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J115">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7F</t>
+          <t xml:space="preserve">Langetoften 7H</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J116">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7H</t>
+          <t xml:space="preserve">Langetoften 7L</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8756,11 +8756,11 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J117">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8816,35 +8816,35 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 7L</t>
+          <t xml:space="preserve">Rolighedsvej 6</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226614</t>
+          <t xml:space="preserve">2224163</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J118">
-        <v>219</v>
+        <v>666</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272658</t>
+          <t xml:space="preserve">311272707</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolighedsvej 6</t>
+          <t xml:space="preserve">Toftekæret 1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224163</t>
+          <t xml:space="preserve">2226957</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,16 +8910,16 @@
         </is>
       </c>
       <c r="J119">
-        <v>666</v>
+        <v>292</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272707</t>
+          <t xml:space="preserve">311272656</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftekæret 1</t>
+          <t xml:space="preserve">Åbanken 22A</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226957</t>
+          <t xml:space="preserve">7833238</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,11 +8985,11 @@
         </is>
       </c>
       <c r="J120">
-        <v>292</v>
+        <v>240</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272656</t>
+          <t xml:space="preserve">311272654</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9041,30 +9041,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbanken 22A</t>
+          <t xml:space="preserve">Skolevej 12</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">7833238</t>
+          <t xml:space="preserve">2222340</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J121">
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272654</t>
+          <t xml:space="preserve">311275664</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-13</t>
+          <t xml:space="preserve">2027-09-28</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9131,15 +9131,15 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J122">
-        <v>192</v>
+        <v>1290</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275664</t>
+          <t xml:space="preserve">311275668</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9206,11 +9206,11 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J123">
-        <v>1290</v>
+        <v>882</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 12</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,20 +9276,20 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222340</t>
+          <t xml:space="preserve">2222743</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J124">
-        <v>882</v>
+        <v>546</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275668</t>
+          <t xml:space="preserve">311275657</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J125">
-        <v>546</v>
+        <v>486</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9431,15 +9431,15 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>486</v>
+        <v>6037</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275657</t>
+          <t xml:space="preserve">311275663</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9506,15 +9506,15 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J127">
-        <v>6037</v>
+        <v>800</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275663</t>
+          <t xml:space="preserve">311275658</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9581,15 +9581,15 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J128">
-        <v>800</v>
+        <v>1491</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275658</t>
+          <t xml:space="preserve">311275884</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-28</t>
+          <t xml:space="preserve">2027-09-29</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9656,11 +9656,11 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J129">
-        <v>1491</v>
+        <v>1280</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -9731,11 +9731,11 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J130">
-        <v>1280</v>
+        <v>592</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Horseager 15</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,20 +9801,20 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222743</t>
+          <t xml:space="preserve">2222743, 100756340</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J131">
-        <v>592</v>
+        <v>147</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311275884</t>
+          <t xml:space="preserve">311276415</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-29</t>
+          <t xml:space="preserve">2027-10-03</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horseager 15</t>
+          <t xml:space="preserve">Horseager 15A</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222743, 100756340</t>
+          <t xml:space="preserve">2222743</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J132">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276415</t>
+          <t xml:space="preserve">311276416</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horseager 15A</t>
+          <t xml:space="preserve">Skolevej 12</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,20 +9951,20 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222743</t>
+          <t xml:space="preserve">2222340</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J133">
-        <v>198</v>
+        <v>570</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276416</t>
+          <t xml:space="preserve">311276413</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10031,15 +10031,15 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J134">
-        <v>570</v>
+        <v>658</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276413</t>
+          <t xml:space="preserve">311276414</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,30 +10091,30 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 12</t>
+          <t xml:space="preserve">Elverdamsvej 204</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2222340</t>
+          <t xml:space="preserve">8459456</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J135">
-        <v>658</v>
+        <v>2619</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311276414</t>
+          <t xml:space="preserve">311280698</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-03</t>
+          <t xml:space="preserve">2027-10-26</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10181,11 +10181,11 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J136">
-        <v>2619</v>
+        <v>1939</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10256,11 +10256,11 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J137">
-        <v>1939</v>
+        <v>2452</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10331,15 +10331,15 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J138">
-        <v>2452</v>
+        <v>595</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280698</t>
+          <t xml:space="preserve">311282470</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-26</t>
+          <t xml:space="preserve">2027-11-07</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elverdamsvej 204</t>
+          <t xml:space="preserve">Elverdamsvej 206</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10406,11 +10406,11 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J139">
-        <v>595</v>
+        <v>2449</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -10466,35 +10466,35 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elverdamsvej 206</t>
+          <t xml:space="preserve">Sonnerup Gade 4</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8459456</t>
+          <t xml:space="preserve">2230776</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>2449</v>
+        <v>180</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282470</t>
+          <t xml:space="preserve">311282473</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sonnerup Gade 4</t>
+          <t xml:space="preserve">Herslevvej 23A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2230776</t>
+          <t xml:space="preserve">2172657</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,21 +10560,21 @@
         </is>
       </c>
       <c r="J141">
-        <v>180</v>
+        <v>2182</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282473</t>
+          <t xml:space="preserve">311285213</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-07</t>
+          <t xml:space="preserve">2027-11-22</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10631,11 +10631,11 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>2182</v>
+        <v>2434</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -10706,11 +10706,11 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J143">
-        <v>2434</v>
+        <v>602</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J144">
-        <v>602</v>
+        <v>906</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10856,11 +10856,11 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J145">
-        <v>906</v>
+        <v>179</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J146">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herslevvej 23A</t>
+          <t xml:space="preserve">Herslevvej 23B</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11006,11 +11006,11 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J147">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herslevvej 23B</t>
+          <t xml:space="preserve">Herslevvej 23C</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,20 +11076,20 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172657</t>
+          <t xml:space="preserve">2172675</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>270</v>
+        <v>2160</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285213</t>
+          <t xml:space="preserve">311285216</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herslevvej 23C</t>
+          <t xml:space="preserve">Bogøvej 11</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172675</t>
+          <t xml:space="preserve">2229011</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,11 +11160,11 @@
         </is>
       </c>
       <c r="J149">
-        <v>2160</v>
+        <v>1057</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285216</t>
+          <t xml:space="preserve">311285668</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-22</t>
+          <t xml:space="preserve">2027-11-24</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J150">
-        <v>1057</v>
+        <v>1610</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11306,11 +11306,11 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J151">
-        <v>1610</v>
+        <v>335</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -11381,15 +11381,15 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J152">
-        <v>335</v>
+        <v>1142</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285668</t>
+          <t xml:space="preserve">311285664</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11456,15 +11456,15 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J153">
-        <v>1142</v>
+        <v>360</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311285664</t>
+          <t xml:space="preserve">311286455</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-24</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11526,20 +11526,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229011</t>
+          <t xml:space="preserve">2229495</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J154">
-        <v>360</v>
+        <v>1085</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286455</t>
+          <t xml:space="preserve">311291937</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2028-01-10</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11606,11 +11606,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J155">
-        <v>1085</v>
+        <v>160</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bogøvej 11</t>
+          <t xml:space="preserve">Bogøvej 13</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,20 +11676,20 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229495</t>
+          <t xml:space="preserve">2229011</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J156">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291937</t>
+          <t xml:space="preserve">311291940</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bogøvej 13</t>
+          <t xml:space="preserve">Fanøvej 2A</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11756,15 +11756,15 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J157">
-        <v>175</v>
+        <v>291</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291940</t>
+          <t xml:space="preserve">311291939</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11831,11 +11831,11 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J158">
-        <v>291</v>
+        <v>731</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fanøvej 2A</t>
+          <t xml:space="preserve">Bygaden 49</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229011</t>
+          <t xml:space="preserve">2223675</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>731</v>
+        <v>188</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291939</t>
+          <t xml:space="preserve">311292384</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-10</t>
+          <t xml:space="preserve">2028-01-12</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 49</t>
+          <t xml:space="preserve">Bygaden 49A</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11981,11 +11981,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J160">
-        <v>188</v>
+        <v>526</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 49A</t>
+          <t xml:space="preserve">Bygaden 51</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12056,15 +12056,15 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J161">
-        <v>526</v>
+        <v>496</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292384</t>
+          <t xml:space="preserve">311292387</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12131,15 +12131,15 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>496</v>
+        <v>1025</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292387</t>
+          <t xml:space="preserve">311292384</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12206,11 +12206,11 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J163">
-        <v>1025</v>
+        <v>809</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12281,11 +12281,11 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J164">
-        <v>809</v>
+        <v>1062</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -12356,15 +12356,15 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J165">
-        <v>1062</v>
+        <v>2086</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292384</t>
+          <t xml:space="preserve">311292386</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12431,11 +12431,11 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J166">
-        <v>2086</v>
+        <v>397</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -12506,11 +12506,11 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J167">
-        <v>397</v>
+        <v>566</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 51</t>
+          <t xml:space="preserve">Bygaden 53</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12581,15 +12581,15 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J168">
-        <v>566</v>
+        <v>1304</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292386</t>
+          <t xml:space="preserve">311292388</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 53</t>
+          <t xml:space="preserve">Ammershøjvej 2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223675</t>
+          <t xml:space="preserve">8383897</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>1304</v>
+        <v>313</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311292388</t>
+          <t xml:space="preserve">311300704</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-12</t>
+          <t xml:space="preserve">2028-03-02</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12731,11 +12731,11 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J170">
-        <v>313</v>
+        <v>106</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjvej 2</t>
+          <t xml:space="preserve">Bramsnæsvigvej 2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8383897</t>
+          <t xml:space="preserve">2228565</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>106</v>
+        <v>600</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300704</t>
+          <t xml:space="preserve">311300715</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>600</v>
+        <v>165</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12956,11 +12956,11 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J173">
-        <v>165</v>
+        <v>344</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13031,11 +13031,11 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J174">
-        <v>344</v>
+        <v>118</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bramsnæsvigvej 2</t>
+          <t xml:space="preserve">Ejby Strandvej 2B</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,20 +13101,20 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228565</t>
+          <t xml:space="preserve">2228222</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300715</t>
+          <t xml:space="preserve">311300711</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejby Strandvej 2B</t>
+          <t xml:space="preserve">Hyllebjerget 2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228222</t>
+          <t xml:space="preserve">2228357</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300711</t>
+          <t xml:space="preserve">311300717</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyllebjerget 2</t>
+          <t xml:space="preserve">Hyllebjerget 4</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228357</t>
+          <t xml:space="preserve">2228358</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -13260,11 +13260,11 @@
         </is>
       </c>
       <c r="J177">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300717</t>
+          <t xml:space="preserve">311300719</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyllebjerget 4</t>
+          <t xml:space="preserve">Landevejen 75</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228358</t>
+          <t xml:space="preserve">722482</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J178">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300719</t>
+          <t xml:space="preserve">311300713</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13391,30 +13391,30 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landevejen 75</t>
+          <t xml:space="preserve">Lyndby Gade 20</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">722482</t>
+          <t xml:space="preserve">7377129</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>137</v>
+        <v>563</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300713</t>
+          <t xml:space="preserve">311300697</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyndby Gade 20</t>
+          <t xml:space="preserve">Stationsvej 14</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">7377129</t>
+          <t xml:space="preserve">2224134</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,11 +13485,11 @@
         </is>
       </c>
       <c r="J180">
-        <v>563</v>
+        <v>349</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300697</t>
+          <t xml:space="preserve">311300706</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 14</t>
+          <t xml:space="preserve">Vintapperbuen 2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224134</t>
+          <t xml:space="preserve">2225331</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -13560,11 +13560,11 @@
         </is>
       </c>
       <c r="J181">
-        <v>349</v>
+        <v>934</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300706</t>
+          <t xml:space="preserve">311300709</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,17 +13616,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vintapperbuen 2</t>
+          <t xml:space="preserve">Ærøvej 1</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225331</t>
+          <t xml:space="preserve">2229031</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,11 +13635,11 @@
         </is>
       </c>
       <c r="J182">
-        <v>934</v>
+        <v>180</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300709</t>
+          <t xml:space="preserve">311300710</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J183">
@@ -13781,11 +13781,11 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J184">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13856,15 +13856,15 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J185">
-        <v>360</v>
+        <v>100</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300710</t>
+          <t xml:space="preserve">311300714</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ærøvej 1</t>
+          <t xml:space="preserve">Ærøvej 13</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,20 +13926,20 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229031</t>
+          <t xml:space="preserve">2229032</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300714</t>
+          <t xml:space="preserve">311300707</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14006,11 +14006,11 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J187">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J188">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J189">
@@ -14231,11 +14231,11 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J190">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14291,30 +14291,30 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ærøvej 13</t>
+          <t xml:space="preserve">Gershøj Havnevej 16</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229032</t>
+          <t xml:space="preserve">2220947</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J191">
-        <v>180</v>
+        <v>550</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311300707</t>
+          <t xml:space="preserve">311302757</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-02</t>
+          <t xml:space="preserve">2028-03-14</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,17 +14366,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gershøj Havnevej 16</t>
+          <t xml:space="preserve">Gevninge Bygade 17B</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220947</t>
+          <t xml:space="preserve">2221238</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>550</v>
+        <v>615</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302757</t>
+          <t xml:space="preserve">311302753</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gevninge Bygade 17B</t>
+          <t xml:space="preserve">Hovedvejen 10D</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,20 +14451,20 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221238</t>
+          <t xml:space="preserve">7903255</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J193">
-        <v>615</v>
+        <v>565</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302753</t>
+          <t xml:space="preserve">311302749</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 10D</t>
+          <t xml:space="preserve">Nødager 30A</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,25 +14526,25 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">7903255</t>
+          <t xml:space="preserve">264048, 264049</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J194">
-        <v>565</v>
+        <v>410</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302749</t>
+          <t xml:space="preserve">311302752</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 30A</t>
+          <t xml:space="preserve">Ammershøjparken 1A</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">264048, 264049</t>
+          <t xml:space="preserve">9767352</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,21 +14610,21 @@
         </is>
       </c>
       <c r="J195">
-        <v>410</v>
+        <v>776</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311302752</t>
+          <t xml:space="preserve">311306915</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-14</t>
+          <t xml:space="preserve">2028-04-06</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjparken 1A</t>
+          <t xml:space="preserve">Ammershøjparken 1B</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14681,7 +14681,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J196">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjparken 1B</t>
+          <t xml:space="preserve">Ammershøjparken 1C</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J197">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjparken 1C</t>
+          <t xml:space="preserve">Ammershøjparken 1D</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J198">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjparken 1D</t>
+          <t xml:space="preserve">Ammershøjparken 1E</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J199">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjparken 1E</t>
+          <t xml:space="preserve">Ammershøjparken 51</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14981,20 +14981,20 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J200">
-        <v>776</v>
+        <v>561</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306915</t>
+          <t xml:space="preserve">311306912</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjparken 51</t>
+          <t xml:space="preserve">Ebbemosen 4</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15051,25 +15051,25 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9767352</t>
+          <t xml:space="preserve">2228376</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J201">
-        <v>561</v>
+        <v>360</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306912</t>
+          <t xml:space="preserve">311306917</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ebbemosen 4</t>
+          <t xml:space="preserve">Elverdamsvej 200</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228376</t>
+          <t xml:space="preserve">263612, 263613</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,11 +15135,11 @@
         </is>
       </c>
       <c r="J202">
-        <v>360</v>
+        <v>3129</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306917</t>
+          <t xml:space="preserve">311306920</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elverdamsvej 200</t>
+          <t xml:space="preserve">Hornsherredvej 202</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">263612, 263613</t>
+          <t xml:space="preserve">2225797</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -15210,11 +15210,11 @@
         </is>
       </c>
       <c r="J203">
-        <v>3129</v>
+        <v>83</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306920</t>
+          <t xml:space="preserve">311306918</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornsherredvej 202</t>
+          <t xml:space="preserve">Pilevej 8</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225797</t>
+          <t xml:space="preserve">8865273</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15285,11 +15285,11 @@
         </is>
       </c>
       <c r="J204">
-        <v>83</v>
+        <v>330</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306918</t>
+          <t xml:space="preserve">311306911</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,17 +15341,17 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilevej 8</t>
+          <t xml:space="preserve">Alfarvejen 13</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">8865273</t>
+          <t xml:space="preserve">2226488</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -15360,11 +15360,11 @@
         </is>
       </c>
       <c r="J205">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306911</t>
+          <t xml:space="preserve">311310399</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-06</t>
+          <t xml:space="preserve">2028-04-25</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,17 +15416,17 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alfarvejen 13</t>
+          <t xml:space="preserve">Alsvej 1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226488</t>
+          <t xml:space="preserve">8106051</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -15435,11 +15435,11 @@
         </is>
       </c>
       <c r="J206">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311310399</t>
+          <t xml:space="preserve">311310400</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 1</t>
+          <t xml:space="preserve">Fjordager 82</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">8106051</t>
+          <t xml:space="preserve">9743518</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>258</v>
+        <v>896</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311310400</t>
+          <t xml:space="preserve">311310396</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15566,17 +15566,17 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordager 82</t>
+          <t xml:space="preserve">Magnolievej 22</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">9743518</t>
+          <t xml:space="preserve">2229441</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -15585,11 +15585,11 @@
         </is>
       </c>
       <c r="J208">
-        <v>896</v>
+        <v>524</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311310396</t>
+          <t xml:space="preserve">311310398</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magnolievej 22</t>
+          <t xml:space="preserve">Skolevang 3</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2229441</t>
+          <t xml:space="preserve">2230723</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,11 +15660,11 @@
         </is>
       </c>
       <c r="J209">
-        <v>524</v>
+        <v>482</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311310398</t>
+          <t xml:space="preserve">311310397</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15716,17 +15716,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevang 3</t>
+          <t xml:space="preserve">Bygaden 20</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2230723</t>
+          <t xml:space="preserve">2220496</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,11 +15735,11 @@
         </is>
       </c>
       <c r="J210">
-        <v>482</v>
+        <v>775</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311310397</t>
+          <t xml:space="preserve">311312604</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-25</t>
+          <t xml:space="preserve">2028-05-07</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 20</t>
+          <t xml:space="preserve">Bøgebakken 2</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15801,20 +15801,20 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220496</t>
+          <t xml:space="preserve">100030959</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J211">
-        <v>775</v>
+        <v>851</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312604</t>
+          <t xml:space="preserve">311312613</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgebakken 2</t>
+          <t xml:space="preserve">Bøgebakken 3</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15881,11 +15881,11 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J212">
-        <v>851</v>
+        <v>604</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgebakken 3</t>
+          <t xml:space="preserve">Bøgebakken 4</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15956,11 +15956,11 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J213">
-        <v>604</v>
+        <v>551</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -16016,30 +16016,30 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgebakken 4</t>
+          <t xml:space="preserve">Hornsherredvej 446B</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030959</t>
+          <t xml:space="preserve">8591191</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J214">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312613</t>
+          <t xml:space="preserve">311312610</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornsherredvej 446B</t>
+          <t xml:space="preserve">Hornsherredvej 446C</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16106,15 +16106,15 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J215">
-        <v>581</v>
+        <v>681</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312610</t>
+          <t xml:space="preserve">311312611</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16166,30 +16166,30 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornsherredvej 446C</t>
+          <t xml:space="preserve">Lejrevej 15</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8591191</t>
+          <t xml:space="preserve">2220454</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J216">
-        <v>681</v>
+        <v>3417</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312611</t>
+          <t xml:space="preserve">311312599</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16241,17 +16241,17 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrevej 15</t>
+          <t xml:space="preserve">Møllebjergvej 4</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220454</t>
+          <t xml:space="preserve">2223225</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -16260,11 +16260,11 @@
         </is>
       </c>
       <c r="J217">
-        <v>3417</v>
+        <v>2773</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312599</t>
+          <t xml:space="preserve">311312602</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16316,17 +16316,17 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebjergvej 4</t>
+          <t xml:space="preserve">Bispegårdsvej 6</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223225</t>
+          <t xml:space="preserve">8242580</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -16335,11 +16335,11 @@
         </is>
       </c>
       <c r="J218">
-        <v>2773</v>
+        <v>245</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311312602</t>
+          <t xml:space="preserve">311314949</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-07</t>
+          <t xml:space="preserve">2028-05-18</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispegårdsvej 6</t>
+          <t xml:space="preserve">Engtoften 22</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">8242580</t>
+          <t xml:space="preserve">2226810</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311314949</t>
+          <t xml:space="preserve">311314950</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16481,11 +16481,11 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J220">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -16556,11 +16556,11 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J221">
-        <v>286</v>
+        <v>120</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engtoften 22</t>
+          <t xml:space="preserve">Engtoften 26</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,20 +16626,20 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226810</t>
+          <t xml:space="preserve">1305766</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J222">
-        <v>120</v>
+        <v>518</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311314950</t>
+          <t xml:space="preserve">311314952</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engtoften 26</t>
+          <t xml:space="preserve">Bøgebakken 1A</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305766</t>
+          <t xml:space="preserve">100030961</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -16710,11 +16710,11 @@
         </is>
       </c>
       <c r="J223">
-        <v>518</v>
+        <v>1457</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311314952</t>
+          <t xml:space="preserve">311315251</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16724,7 +16724,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-18</t>
+          <t xml:space="preserve">2028-05-22</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,17 +16766,17 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgebakken 1A</t>
+          <t xml:space="preserve">Klostergårdsvej 4</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030961</t>
+          <t xml:space="preserve">2171115</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -16785,11 +16785,11 @@
         </is>
       </c>
       <c r="J224">
-        <v>1457</v>
+        <v>626</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315251</t>
+          <t xml:space="preserve">311316930</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-22</t>
+          <t xml:space="preserve">2028-05-29</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostergårdsvej 4</t>
+          <t xml:space="preserve">Hovedvejen 10B</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16851,20 +16851,20 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171115</t>
+          <t xml:space="preserve">7903255</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J225">
-        <v>626</v>
+        <v>192</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311316930</t>
+          <t xml:space="preserve">311318644</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-29</t>
+          <t xml:space="preserve">2028-06-06</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 10B</t>
+          <t xml:space="preserve">Hovedvejen 10C</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16931,15 +16931,15 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J226">
-        <v>192</v>
+        <v>362</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311318644</t>
+          <t xml:space="preserve">311318646</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 10C</t>
+          <t xml:space="preserve">Hovedvejen 10D</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17006,15 +17006,15 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>362</v>
+        <v>1614</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311318646</t>
+          <t xml:space="preserve">311318648</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17066,17 +17066,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 10D</t>
+          <t xml:space="preserve">Smedegården 13</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">7903255</t>
+          <t xml:space="preserve">2220366</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -17085,11 +17085,11 @@
         </is>
       </c>
       <c r="J228">
-        <v>1614</v>
+        <v>331</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311318648</t>
+          <t xml:space="preserve">311318898</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegården 13</t>
+          <t xml:space="preserve">Bøgebakken 1</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220366</t>
+          <t xml:space="preserve">100030958</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,11 +17160,11 @@
         </is>
       </c>
       <c r="J229">
-        <v>331</v>
+        <v>4947</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311318898</t>
+          <t xml:space="preserve">311319190</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-06</t>
+          <t xml:space="preserve">2028-06-07</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgebakken 1</t>
+          <t xml:space="preserve">Flædevadsvej 2</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17226,20 +17226,20 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">100030958</t>
+          <t xml:space="preserve">2220496</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J230">
-        <v>4947</v>
+        <v>212</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319190</t>
+          <t xml:space="preserve">311319187</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17291,30 +17291,30 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flædevadsvej 2</t>
+          <t xml:space="preserve">Nødager 32</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220496</t>
+          <t xml:space="preserve">100023432</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J231">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319187</t>
+          <t xml:space="preserve">311319189</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17381,15 +17381,15 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J232">
-        <v>152</v>
+        <v>304</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319189</t>
+          <t xml:space="preserve">311319188</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 32</t>
+          <t xml:space="preserve">Nødager 36</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17456,15 +17456,15 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J233">
-        <v>304</v>
+        <v>210</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319188</t>
+          <t xml:space="preserve">311319189</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 36</t>
+          <t xml:space="preserve">Nødager 42</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17531,11 +17531,11 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J234">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 42</t>
+          <t xml:space="preserve">Nødager 46</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17606,11 +17606,11 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J235">
-        <v>152</v>
+        <v>234</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 46</t>
+          <t xml:space="preserve">Nødager 60</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17681,15 +17681,15 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J236">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319189</t>
+          <t xml:space="preserve">311319188</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 60</t>
+          <t xml:space="preserve">Nødager 66</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17756,11 +17756,11 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J237">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -17816,30 +17816,30 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nødager 66</t>
+          <t xml:space="preserve">Bispegårdsvej 4</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">100023432</t>
+          <t xml:space="preserve">2220374</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J238">
-        <v>292</v>
+        <v>3029</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319188</t>
+          <t xml:space="preserve">311336541</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-07</t>
+          <t xml:space="preserve">2028-09-17</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,40 +17891,40 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispegårdsvej 4</t>
+          <t xml:space="preserve">Hyllebjerget 6</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220374</t>
+          <t xml:space="preserve">2228359</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>3029</v>
+        <v>112</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336541</t>
+          <t xml:space="preserve">311337161</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Boligeftersyn P/S</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-17</t>
+          <t xml:space="preserve">2028-09-20</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,17 +17966,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyllebjerget 6</t>
+          <t xml:space="preserve">Bispegårdsvej 2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228359</t>
+          <t xml:space="preserve">2220374</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,21 +17985,21 @@
         </is>
       </c>
       <c r="J240">
-        <v>112</v>
+        <v>7779</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337161</t>
+          <t xml:space="preserve">311337585</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligeftersyn P/S</t>
+          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-20</t>
+          <t xml:space="preserve">2028-09-21</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,17 +18041,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispegårdsvej 2</t>
+          <t xml:space="preserve">Ammershøjparken 1G</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220374</t>
+          <t xml:space="preserve">100321678</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -18060,21 +18060,21 @@
         </is>
       </c>
       <c r="J241">
-        <v>7779</v>
+        <v>1891</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337585</t>
+          <t xml:space="preserve">311575809</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">TT-Energioptimering</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-21</t>
+          <t xml:space="preserve">2032-01-31</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ammershøjparken 1G</t>
+          <t xml:space="preserve">Ebbemosevej 1</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18126,30 +18126,30 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">100321678</t>
+          <t xml:space="preserve">100418468</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J242">
-        <v>1891</v>
+        <v>1135</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575809</t>
+          <t xml:space="preserve">311609041</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">TT-Energioptimering</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-31</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ebbemosevej 1</t>
+          <t xml:space="preserve">Bygaden 28A</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18201,30 +18201,30 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">100418468</t>
+          <t xml:space="preserve">2223861</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J243">
-        <v>1135</v>
+        <v>135</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609041</t>
+          <t xml:space="preserve">311612696</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-07-04</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 28A</t>
+          <t xml:space="preserve">Karlebyvej 130A</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,12 +18276,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223861</t>
+          <t xml:space="preserve">2225368</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J244">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612696</t>
+          <t xml:space="preserve">311612697</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlebyvej 130A</t>
+          <t xml:space="preserve">Møllevej 2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,12 +18351,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2225368</t>
+          <t xml:space="preserve">2223859</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612697</t>
+          <t xml:space="preserve">311612695</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18416,40 +18416,40 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevej 2</t>
+          <t xml:space="preserve">Hovedvejen 124A</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4070</t>
+          <t xml:space="preserve">4320</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223859</t>
+          <t xml:space="preserve">2226592</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J246">
-        <v>135</v>
+        <v>346</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612695</t>
+          <t xml:space="preserve">311661245</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-04</t>
+          <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 124A</t>
+          <t xml:space="preserve">Hovedvejen 124B</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18506,11 +18506,11 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J247">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvejen 124B</t>
+          <t xml:space="preserve">Langetoften 25</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18581,11 +18581,11 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J248">
-        <v>362</v>
+        <v>3904</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -18656,11 +18656,11 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J249">
-        <v>3904</v>
+        <v>1284</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -18731,11 +18731,11 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J250">
-        <v>1284</v>
+        <v>642</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -18806,11 +18806,11 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J251">
-        <v>642</v>
+        <v>1284</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
@@ -18881,11 +18881,11 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J252">
-        <v>1284</v>
+        <v>275</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 25</t>
+          <t xml:space="preserve">Langetoften 27</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18956,11 +18956,11 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J253">
-        <v>275</v>
+        <v>1998</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 27</t>
+          <t xml:space="preserve">Langetoften 25</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19031,25 +19031,25 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J254">
-        <v>1998</v>
+        <v>951</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661245</t>
+          <t xml:space="preserve">311685608</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-20</t>
+          <t xml:space="preserve">2033-06-06</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,40 +19091,40 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langetoften 25</t>
+          <t xml:space="preserve">Klostergårdsvej 5A</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2226592</t>
+          <t xml:space="preserve">2171129</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J255">
-        <v>951</v>
+        <v>112</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311685608</t>
+          <t xml:space="preserve">311739357</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-06</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,17 +19166,17 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostergårdsvej 5A</t>
+          <t xml:space="preserve">Møllebjergvej 2</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4330</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2171129</t>
+          <t xml:space="preserve">2223212</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,21 +19185,21 @@
         </is>
       </c>
       <c r="J256">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739357</t>
+          <t xml:space="preserve">311751601</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve">Domutech Solutions A/S</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-04-12</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,17 +19241,17 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllebjergvej 2</t>
+          <t xml:space="preserve">Herslevvej 25</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">4330</t>
+          <t xml:space="preserve">4000</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2223212</t>
+          <t xml:space="preserve">2172679</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -19260,21 +19260,21 @@
         </is>
       </c>
       <c r="J257">
-        <v>164</v>
+        <v>1060</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751601</t>
+          <t xml:space="preserve">311865603</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech Solutions A/S</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-12</t>
+          <t xml:space="preserve">2035-10-31</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,40 +19316,40 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herslevvej 25</t>
+          <t xml:space="preserve">Skolevang 1</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000</t>
+          <t xml:space="preserve">4060</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2172679</t>
+          <t xml:space="preserve">2230678</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J258">
-        <v>1060</v>
+        <v>308</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311865603</t>
+          <t xml:space="preserve">311922173</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-31</t>
+          <t xml:space="preserve">2036-08-27</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19406,15 +19406,15 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J259">
-        <v>308</v>
+        <v>2596</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922173</t>
+          <t xml:space="preserve">311922276</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-27</t>
+          <t xml:space="preserve">2036-08-28</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19481,11 +19481,11 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J260">
-        <v>2596</v>
+        <v>590</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -19541,30 +19541,30 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevang 1</t>
+          <t xml:space="preserve">Karlebyvej 58</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">4060</t>
+          <t xml:space="preserve">4070</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2230678</t>
+          <t xml:space="preserve">8865239</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J261">
-        <v>590</v>
+        <v>1058</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922276</t>
+          <t xml:space="preserve">311922594</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-28</t>
+          <t xml:space="preserve">2036-08-31</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Karlebyvej 58</t>
+          <t xml:space="preserve">Bygaden 35</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">8865239</t>
+          <t xml:space="preserve">2224218</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -19635,11 +19635,11 @@
         </is>
       </c>
       <c r="J262">
-        <v>1058</v>
+        <v>62</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311922594</t>
+          <t xml:space="preserve">311930045</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-31</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
